--- a/excel/1000(n)/AVG_ReverseSort_Dataset.xlsx
+++ b/excel/1000(n)/AVG_ReverseSort_Dataset.xlsx
@@ -102,19 +102,19 @@
         <v>1000.0</v>
       </c>
       <c r="B2" t="n" s="0">
-        <v>770185.0</v>
+        <v>584790.0</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>329310.0</v>
+        <v>102655.0</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>937045.0</v>
+        <v>942800.0</v>
       </c>
       <c r="E2" t="n" s="0">
-        <v>77265.0</v>
+        <v>53420.0</v>
       </c>
       <c r="F2" t="n" s="0">
-        <v>85985.0</v>
+        <v>69790.0</v>
       </c>
     </row>
   </sheetData>

--- a/excel/1000(n)/AVG_ReverseSort_Dataset.xlsx
+++ b/excel/1000(n)/AVG_ReverseSort_Dataset.xlsx
@@ -102,19 +102,19 @@
         <v>1000.0</v>
       </c>
       <c r="B2" t="n" s="0">
-        <v>584790.0</v>
+        <v>535055.0</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>102655.0</v>
+        <v>128825.0</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>942800.0</v>
+        <v>946435.0</v>
       </c>
       <c r="E2" t="n" s="0">
-        <v>53420.0</v>
+        <v>323630.0</v>
       </c>
       <c r="F2" t="n" s="0">
-        <v>69790.0</v>
+        <v>70035.0</v>
       </c>
     </row>
   </sheetData>
